--- a/Results_2024Pricing/Figures_Analysis/Tradeoffs.xlsx
+++ b/Results_2024Pricing/Figures_Analysis/Tradeoffs.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="717" firstSheet="1" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="-120" windowWidth="28800" windowHeight="11100" tabRatio="717" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Offset_2024Pricing" sheetId="64" r:id="rId1"/>
@@ -20013,14 +20013,14 @@
       <sheetName val="$20MWh_Market"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
       <sheetData sheetId="8">
         <row r="6">
           <cell r="B6">
@@ -20995,14 +20995,14 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="15" refreshError="1"/>
+      <sheetData sheetId="16" refreshError="1"/>
+      <sheetData sheetId="17" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
